--- a/reports/Debug-snowbowl-20260106/For The Day (Prior Year)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20260106/For The Day (Prior Year)_Visits.xlsx
@@ -448,7 +448,7 @@
         <v>45664</v>
       </c>
       <c r="C3" s="2">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -518,7 +518,7 @@
         <v>45664</v>
       </c>
       <c r="C8" s="2">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>6</v>
